--- a/network_equipment.xlsx
+++ b/network_equipment.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2618" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2618" uniqueCount="683">
   <si>
     <t xml:space="preserve">NVIDIA Network Equipment</t>
   </si>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Snapshot</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-24</t>
+    <t xml:space="preserve">2026-10-25</t>
   </si>
   <si>
     <t xml:space="preserve">Schema</t>
@@ -1467,6 +1467,12 @@
     <t xml:space="preserve">InfiniBand-to-Ethernet Gateway</t>
   </si>
   <si>
+    <t xml:space="preserve">MGA100-HS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">920-9B020-00FA-0D2</t>
+  </si>
+  <si>
     <t xml:space="preserve">100/200 Gb/s per port</t>
   </si>
   <si>
@@ -1479,7 +1485,7 @@
     <t xml:space="preserve">https://networking-docs.nvidia.com/skyway</t>
   </si>
   <si>
-    <t xml:space="preserve">InfiniBand switching / appliances / gateways Skyway  InfiniBand-to-Ethernet Gateway documented — — 100/200 Gb/s per port  8x QSFP56 100/200 Gb/s [InfiniBand]; 8x QSFP56 100/200 Gb/s [Ethernet]    InfiniBand-to-Ethernet Gateway 100/200 Gb/s per port: 8 ports per InfiniBand and Ethernet side</t>
+    <t xml:space="preserve">InfiniBand switching / appliances / gateways Skyway  InfiniBand-to-Ethernet Gateway documented MGA100-HS2 920-9B020-00FA-0D2 100/200 Gb/s per port  8x QSFP56 100/200 Gb/s [InfiniBand]; 8x QSFP56 100/200 Gb/s [Ethernet]    InfiniBand-to-Ethernet Gateway 100/200 Gb/s per port: 8 ports per InfiniBand and Ethernet side</t>
   </si>
   <si>
     <t xml:space="preserve">MetroX-3 XC</t>
@@ -2217,44 +2223,40 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2610,12 +2612,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2623,7 +2625,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -2631,7 +2633,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -2639,7 +2641,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -2674,7 +2676,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
@@ -2694,7 +2696,7 @@
         <v>16</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>22</v>
@@ -2703,12 +2705,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>458</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>364</v>
@@ -2726,18 +2728,18 @@
         <v>461</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -2749,16 +2751,16 @@
         <v>30</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
   </sheetData>
@@ -2795,7 +2797,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
@@ -2815,7 +2817,7 @@
         <v>16</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>22</v>
@@ -2824,9 +2826,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>30</v>
@@ -2841,21 +2843,21 @@
         <v>30</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>30</v>
@@ -2876,15 +2878,15 @@
         <v>30</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>30</v>
@@ -2896,19 +2898,19 @@
         <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
   </sheetData>
@@ -2946,7 +2948,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="48"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
@@ -2966,7 +2968,7 @@
         <v>16</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>22</v>
@@ -2975,9 +2977,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>30</v>
@@ -2989,24 +2991,24 @@
         <v>30</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>30</v>
@@ -3018,24 +3020,24 @@
         <v>30</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>30</v>
@@ -3047,19 +3049,19 @@
         <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
   </sheetData>
@@ -3097,7 +3099,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="48"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
@@ -3117,108 +3119,108 @@
         <v>16</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>555</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>553</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>566</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -3227,56 +3229,56 @@
         <v>30</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>364</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>364</v>
@@ -3288,24 +3290,24 @@
         <v>30</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>364</v>
@@ -3317,24 +3319,24 @@
         <v>30</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>364</v>
@@ -3346,19 +3348,19 @@
         <v>30</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>590</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <autoFilter ref="A1:I9"/>
   <hyperlinks>
@@ -3399,7 +3401,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
@@ -3416,7 +3418,7 @@
         <v>15</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>22</v>
@@ -3425,12 +3427,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>364</v>
@@ -3442,169 +3444,169 @@
         <v>30</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>364</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>364</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>364</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>364</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>364</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
   </sheetData>
@@ -3644,7 +3646,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="48"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
@@ -3658,78 +3660,78 @@
         <v>16</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>657</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>129</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F4"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="https://networking-docs.nvidia.com/connectx5enhw"/>
-    <hyperlink ref="F3" r:id="rId2" display="https://networking-docs.nvidia.com/connectx4vpihw"/>
-    <hyperlink ref="F4" r:id="rId3" display="https://networking-docs.nvidia.com/connectx4lxhw"/>
+    <hyperlink ref="F2" r:id="rId1" display="https://networking-docs.nvidia.com/connectx5en"/>
+    <hyperlink ref="F3" r:id="rId2" display="https://networking-docs.nvidia.com/connectx4"/>
+    <hyperlink ref="F4" r:id="rId3" display="https://networking-docs.nvidia.com/connectx4lx"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3767,7 +3769,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
@@ -3820,7 +3822,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -3863,7 +3865,7 @@
       <c r="O2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="1" t="s">
         <v>40</v>
       </c>
       <c r="Q2" s="1" t="str">
@@ -3871,7 +3873,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -3914,7 +3916,7 @@
       <c r="O3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="1" t="s">
         <v>44</v>
       </c>
       <c r="Q3" s="1" t="str">
@@ -3922,7 +3924,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>26</v>
       </c>
@@ -3965,7 +3967,7 @@
       <c r="O4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="1" t="s">
         <v>51</v>
       </c>
       <c r="Q4" s="1" t="str">
@@ -3973,7 +3975,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
@@ -4016,7 +4018,7 @@
       <c r="O5" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="1" t="s">
         <v>54</v>
       </c>
       <c r="Q5" s="1" t="str">
@@ -4024,7 +4026,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
@@ -4067,7 +4069,7 @@
       <c r="O6" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="P6" s="6" t="s">
+      <c r="P6" s="1" t="s">
         <v>58</v>
       </c>
       <c r="Q6" s="1" t="str">
@@ -4075,7 +4077,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
@@ -4118,7 +4120,7 @@
       <c r="O7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="P7" s="6" t="s">
+      <c r="P7" s="1" t="s">
         <v>61</v>
       </c>
       <c r="Q7" s="1" t="str">
@@ -4126,7 +4128,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>26</v>
       </c>
@@ -4169,7 +4171,7 @@
       <c r="O8" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="P8" s="6" t="s">
+      <c r="P8" s="1" t="s">
         <v>67</v>
       </c>
       <c r="Q8" s="1" t="str">
@@ -4177,7 +4179,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
@@ -4220,7 +4222,7 @@
       <c r="O9" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="P9" s="6" t="s">
+      <c r="P9" s="1" t="s">
         <v>71</v>
       </c>
       <c r="Q9" s="1" t="str">
@@ -4228,7 +4230,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
@@ -4271,7 +4273,7 @@
       <c r="O10" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="P10" s="6" t="s">
+      <c r="P10" s="1" t="s">
         <v>79</v>
       </c>
       <c r="Q10" s="1" t="str">
@@ -4279,7 +4281,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
@@ -4322,7 +4324,7 @@
       <c r="O11" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="P11" s="6" t="s">
+      <c r="P11" s="1" t="s">
         <v>81</v>
       </c>
       <c r="Q11" s="1" t="str">
@@ -4330,7 +4332,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>26</v>
       </c>
@@ -4373,7 +4375,7 @@
       <c r="O12" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="P12" s="6" t="s">
+      <c r="P12" s="1" t="s">
         <v>91</v>
       </c>
       <c r="Q12" s="1" t="str">
@@ -4381,7 +4383,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>26</v>
       </c>
@@ -4424,7 +4426,7 @@
       <c r="O13" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="P13" s="6" t="s">
+      <c r="P13" s="1" t="s">
         <v>97</v>
       </c>
       <c r="Q13" s="1" t="str">
@@ -4432,7 +4434,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -4475,7 +4477,7 @@
       <c r="O14" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="P14" s="6" t="s">
+      <c r="P14" s="1" t="s">
         <v>103</v>
       </c>
       <c r="Q14" s="1" t="str">
@@ -4483,7 +4485,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
@@ -4526,7 +4528,7 @@
       <c r="O15" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="P15" s="6" t="s">
+      <c r="P15" s="1" t="s">
         <v>108</v>
       </c>
       <c r="Q15" s="1" t="str">
@@ -4534,7 +4536,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
@@ -4577,7 +4579,7 @@
       <c r="O16" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="P16" s="6" t="s">
+      <c r="P16" s="1" t="s">
         <v>114</v>
       </c>
       <c r="Q16" s="1" t="str">
@@ -4585,7 +4587,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
@@ -4628,7 +4630,7 @@
       <c r="O17" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="P17" s="6" t="s">
+      <c r="P17" s="1" t="s">
         <v>119</v>
       </c>
       <c r="Q17" s="1" t="str">
@@ -4636,7 +4638,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
@@ -4679,7 +4681,7 @@
       <c r="O18" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="P18" s="6" t="s">
+      <c r="P18" s="1" t="s">
         <v>125</v>
       </c>
       <c r="Q18" s="1" t="str">
@@ -4687,7 +4689,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
@@ -4730,7 +4732,7 @@
       <c r="O19" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="P19" s="6" t="s">
+      <c r="P19" s="1" t="s">
         <v>133</v>
       </c>
       <c r="Q19" s="1" t="str">
@@ -4738,7 +4740,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
@@ -4781,7 +4783,7 @@
       <c r="O20" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="P20" s="6" t="s">
+      <c r="P20" s="1" t="s">
         <v>140</v>
       </c>
       <c r="Q20" s="1" t="str">
@@ -4789,7 +4791,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>26</v>
       </c>
@@ -4832,7 +4834,7 @@
       <c r="O21" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="P21" s="6" t="s">
+      <c r="P21" s="1" t="s">
         <v>149</v>
       </c>
       <c r="Q21" s="1" t="str">
@@ -4840,7 +4842,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>26</v>
       </c>
@@ -4883,7 +4885,7 @@
       <c r="O22" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="P22" s="6" t="s">
+      <c r="P22" s="1" t="s">
         <v>155</v>
       </c>
       <c r="Q22" s="1" t="str">
@@ -4891,7 +4893,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
@@ -4934,7 +4936,7 @@
       <c r="O23" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="P23" s="6" t="s">
+      <c r="P23" s="1" t="s">
         <v>161</v>
       </c>
       <c r="Q23" s="1" t="str">
@@ -4942,7 +4944,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>26</v>
       </c>
@@ -4985,7 +4987,7 @@
       <c r="O24" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="P24" s="6" t="s">
+      <c r="P24" s="1" t="s">
         <v>165</v>
       </c>
       <c r="Q24" s="1" t="str">
@@ -4993,7 +4995,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
@@ -5036,7 +5038,7 @@
       <c r="O25" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="P25" s="6" t="s">
+      <c r="P25" s="1" t="s">
         <v>171</v>
       </c>
       <c r="Q25" s="1" t="str">
@@ -5044,7 +5046,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
@@ -5087,7 +5089,7 @@
       <c r="O26" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="P26" s="6" t="s">
+      <c r="P26" s="1" t="s">
         <v>176</v>
       </c>
       <c r="Q26" s="1" t="str">
@@ -5095,7 +5097,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
@@ -5138,7 +5140,7 @@
       <c r="O27" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="P27" s="6" t="s">
+      <c r="P27" s="1" t="s">
         <v>179</v>
       </c>
       <c r="Q27" s="1" t="str">
@@ -5146,7 +5148,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>26</v>
       </c>
@@ -5189,7 +5191,7 @@
       <c r="O28" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="P28" s="6" t="s">
+      <c r="P28" s="1" t="s">
         <v>184</v>
       </c>
       <c r="Q28" s="1" t="str">
@@ -5197,7 +5199,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>26</v>
       </c>
@@ -5240,7 +5242,7 @@
       <c r="O29" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="P29" s="6" t="s">
+      <c r="P29" s="1" t="s">
         <v>189</v>
       </c>
       <c r="Q29" s="1" t="str">
@@ -5248,7 +5250,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>26</v>
       </c>
@@ -5291,7 +5293,7 @@
       <c r="O30" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="P30" s="6" t="s">
+      <c r="P30" s="1" t="s">
         <v>194</v>
       </c>
       <c r="Q30" s="1" t="str">
@@ -5299,7 +5301,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>26</v>
       </c>
@@ -5342,7 +5344,7 @@
       <c r="O31" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="P31" s="6" t="s">
+      <c r="P31" s="1" t="s">
         <v>200</v>
       </c>
       <c r="Q31" s="1" t="str">
@@ -5350,7 +5352,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>26</v>
       </c>
@@ -5393,7 +5395,7 @@
       <c r="O32" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="P32" s="6" t="s">
+      <c r="P32" s="1" t="s">
         <v>207</v>
       </c>
       <c r="Q32" s="1" t="str">
@@ -5401,7 +5403,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>26</v>
       </c>
@@ -5444,7 +5446,7 @@
       <c r="O33" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="P33" s="6" t="s">
+      <c r="P33" s="1" t="s">
         <v>212</v>
       </c>
       <c r="Q33" s="1" t="str">
@@ -5452,7 +5454,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>26</v>
       </c>
@@ -5495,7 +5497,7 @@
       <c r="O34" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="P34" s="6" t="s">
+      <c r="P34" s="1" t="s">
         <v>219</v>
       </c>
       <c r="Q34" s="1" t="str">
@@ -5503,7 +5505,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>26</v>
       </c>
@@ -5546,7 +5548,7 @@
       <c r="O35" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="P35" s="6" t="s">
+      <c r="P35" s="1" t="s">
         <v>226</v>
       </c>
       <c r="Q35" s="1" t="str">
@@ -5554,7 +5556,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>227</v>
       </c>
@@ -5597,7 +5599,7 @@
       <c r="O36" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="P36" s="6" t="s">
+      <c r="P36" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Q36" s="1" t="str">
@@ -5605,7 +5607,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>227</v>
       </c>
@@ -5648,7 +5650,7 @@
       <c r="O37" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="P37" s="6" t="s">
+      <c r="P37" s="1" t="s">
         <v>243</v>
       </c>
       <c r="Q37" s="1" t="str">
@@ -5656,7 +5658,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>227</v>
       </c>
@@ -5699,7 +5701,7 @@
       <c r="O38" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="P38" s="6" t="s">
+      <c r="P38" s="1" t="s">
         <v>250</v>
       </c>
       <c r="Q38" s="1" t="str">
@@ -5707,7 +5709,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>251</v>
       </c>
@@ -5750,7 +5752,7 @@
       <c r="O39" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="P39" s="6" t="s">
+      <c r="P39" s="1" t="s">
         <v>261</v>
       </c>
       <c r="Q39" s="1" t="str">
@@ -5758,7 +5760,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>251</v>
       </c>
@@ -5801,7 +5803,7 @@
       <c r="O40" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="P40" s="6" t="s">
+      <c r="P40" s="1" t="s">
         <v>269</v>
       </c>
       <c r="Q40" s="1" t="str">
@@ -5809,7 +5811,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>251</v>
       </c>
@@ -5852,7 +5854,7 @@
       <c r="O41" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="P41" s="6" t="s">
+      <c r="P41" s="1" t="s">
         <v>278</v>
       </c>
       <c r="Q41" s="1" t="str">
@@ -5860,7 +5862,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>251</v>
       </c>
@@ -5903,7 +5905,7 @@
       <c r="O42" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="P42" s="6" t="s">
+      <c r="P42" s="1" t="s">
         <v>286</v>
       </c>
       <c r="Q42" s="1" t="str">
@@ -5911,7 +5913,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>251</v>
       </c>
@@ -5954,7 +5956,7 @@
       <c r="O43" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="P43" s="6" t="s">
+      <c r="P43" s="1" t="s">
         <v>291</v>
       </c>
       <c r="Q43" s="1" t="str">
@@ -5962,7 +5964,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>251</v>
       </c>
@@ -6005,7 +6007,7 @@
       <c r="O44" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="P44" s="6" t="s">
+      <c r="P44" s="1" t="s">
         <v>297</v>
       </c>
       <c r="Q44" s="1" t="str">
@@ -6013,7 +6015,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>251</v>
       </c>
@@ -6056,7 +6058,7 @@
       <c r="O45" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="P45" s="6" t="s">
+      <c r="P45" s="1" t="s">
         <v>303</v>
       </c>
       <c r="Q45" s="1" t="str">
@@ -6064,7 +6066,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>251</v>
       </c>
@@ -6107,7 +6109,7 @@
       <c r="O46" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="P46" s="6" t="s">
+      <c r="P46" s="1" t="s">
         <v>307</v>
       </c>
       <c r="Q46" s="1" t="str">
@@ -6115,7 +6117,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>251</v>
       </c>
@@ -6158,7 +6160,7 @@
       <c r="O47" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="P47" s="6" t="s">
+      <c r="P47" s="1" t="s">
         <v>314</v>
       </c>
       <c r="Q47" s="1" t="str">
@@ -6166,7 +6168,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>251</v>
       </c>
@@ -6209,7 +6211,7 @@
       <c r="O48" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="P48" s="6" t="s">
+      <c r="P48" s="1" t="s">
         <v>320</v>
       </c>
       <c r="Q48" s="1" t="str">
@@ -6217,7 +6219,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>251</v>
       </c>
@@ -6260,7 +6262,7 @@
       <c r="O49" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="P49" s="6" t="s">
+      <c r="P49" s="1" t="s">
         <v>326</v>
       </c>
       <c r="Q49" s="1" t="str">
@@ -6268,7 +6270,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
         <v>327</v>
       </c>
@@ -6296,7 +6298,7 @@
       <c r="O50" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="P50" s="6" t="s">
+      <c r="P50" s="1" t="s">
         <v>331</v>
       </c>
       <c r="Q50" s="1" t="str">
@@ -6304,7 +6306,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
         <v>327</v>
       </c>
@@ -6332,7 +6334,7 @@
       <c r="O51" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="P51" s="6" t="s">
+      <c r="P51" s="1" t="s">
         <v>337</v>
       </c>
       <c r="Q51" s="1" t="str">
@@ -6340,7 +6342,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
         <v>327</v>
       </c>
@@ -6368,7 +6370,7 @@
       <c r="O52" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="P52" s="6" t="s">
+      <c r="P52" s="1" t="s">
         <v>341</v>
       </c>
       <c r="Q52" s="1" t="str">
@@ -6376,7 +6378,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
         <v>327</v>
       </c>
@@ -6404,7 +6406,7 @@
       <c r="O53" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="P53" s="6" t="s">
+      <c r="P53" s="1" t="s">
         <v>346</v>
       </c>
       <c r="Q53" s="1" t="str">
@@ -6412,7 +6414,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
         <v>327</v>
       </c>
@@ -6440,7 +6442,7 @@
       <c r="O54" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="P54" s="6" t="s">
+      <c r="P54" s="1" t="s">
         <v>350</v>
       </c>
       <c r="Q54" s="1" t="str">
@@ -6448,7 +6450,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
         <v>327</v>
       </c>
@@ -6476,7 +6478,7 @@
       <c r="O55" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="P55" s="6" t="s">
+      <c r="P55" s="1" t="s">
         <v>354</v>
       </c>
       <c r="Q55" s="1" t="str">
@@ -6484,7 +6486,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
         <v>327</v>
       </c>
@@ -6512,7 +6514,7 @@
       <c r="O56" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="P56" s="6" t="s">
+      <c r="P56" s="1" t="s">
         <v>360</v>
       </c>
       <c r="Q56" s="1" t="str">
@@ -6520,7 +6522,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
         <v>361</v>
       </c>
@@ -6551,7 +6553,7 @@
       <c r="O57" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="P57" s="6" t="s">
+      <c r="P57" s="1" t="s">
         <v>369</v>
       </c>
       <c r="Q57" s="1" t="str">
@@ -6559,7 +6561,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
         <v>361</v>
       </c>
@@ -6590,7 +6592,7 @@
       <c r="O58" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="P58" s="6" t="s">
+      <c r="P58" s="1" t="s">
         <v>374</v>
       </c>
       <c r="Q58" s="1" t="str">
@@ -6598,7 +6600,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
         <v>361</v>
       </c>
@@ -6629,7 +6631,7 @@
       <c r="O59" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="P59" s="6" t="s">
+      <c r="P59" s="1" t="s">
         <v>378</v>
       </c>
       <c r="Q59" s="1" t="str">
@@ -6637,7 +6639,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
         <v>361</v>
       </c>
@@ -6668,7 +6670,7 @@
       <c r="O60" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="P60" s="6" t="s">
+      <c r="P60" s="1" t="s">
         <v>381</v>
       </c>
       <c r="Q60" s="1" t="str">
@@ -6676,7 +6678,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
         <v>361</v>
       </c>
@@ -6707,7 +6709,7 @@
       <c r="O61" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="P61" s="6" t="s">
+      <c r="P61" s="1" t="s">
         <v>388</v>
       </c>
       <c r="Q61" s="1" t="str">
@@ -6715,7 +6717,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
         <v>361</v>
       </c>
@@ -6746,7 +6748,7 @@
       <c r="O62" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="P62" s="6" t="s">
+      <c r="P62" s="1" t="s">
         <v>394</v>
       </c>
       <c r="Q62" s="1" t="str">
@@ -6754,7 +6756,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
         <v>361</v>
       </c>
@@ -6785,7 +6787,7 @@
       <c r="O63" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="P63" s="6" t="s">
+      <c r="P63" s="1" t="s">
         <v>397</v>
       </c>
       <c r="Q63" s="1" t="str">
@@ -6793,7 +6795,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
         <v>361</v>
       </c>
@@ -6824,7 +6826,7 @@
       <c r="O64" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="P64" s="6" t="s">
+      <c r="P64" s="1" t="s">
         <v>403</v>
       </c>
       <c r="Q64" s="1" t="str">
@@ -6832,7 +6834,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
         <v>361</v>
       </c>
@@ -6863,7 +6865,7 @@
       <c r="O65" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="P65" s="6" t="s">
+      <c r="P65" s="1" t="s">
         <v>412</v>
       </c>
       <c r="Q65" s="1" t="str">
@@ -6871,7 +6873,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
         <v>361</v>
       </c>
@@ -6902,7 +6904,7 @@
       <c r="O66" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="P66" s="6" t="s">
+      <c r="P66" s="1" t="s">
         <v>418</v>
       </c>
       <c r="Q66" s="1" t="str">
@@ -6910,7 +6912,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
         <v>361</v>
       </c>
@@ -6941,7 +6943,7 @@
       <c r="O67" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="P67" s="6" t="s">
+      <c r="P67" s="1" t="s">
         <v>426</v>
       </c>
       <c r="Q67" s="1" t="str">
@@ -6949,7 +6951,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
         <v>361</v>
       </c>
@@ -6980,7 +6982,7 @@
       <c r="O68" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="P68" s="6" t="s">
+      <c r="P68" s="1" t="s">
         <v>434</v>
       </c>
       <c r="Q68" s="1" t="str">
@@ -6988,7 +6990,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
         <v>361</v>
       </c>
@@ -7019,7 +7021,7 @@
       <c r="O69" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="P69" s="6" t="s">
+      <c r="P69" s="1" t="s">
         <v>436</v>
       </c>
       <c r="Q69" s="1" t="str">
@@ -7027,7 +7029,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
         <v>361</v>
       </c>
@@ -7058,7 +7060,7 @@
       <c r="O70" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="P70" s="6" t="s">
+      <c r="P70" s="1" t="s">
         <v>440</v>
       </c>
       <c r="Q70" s="1" t="str">
@@ -7066,7 +7068,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
         <v>441</v>
       </c>
@@ -7097,7 +7099,7 @@
       <c r="O71" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="P71" s="6" t="s">
+      <c r="P71" s="1" t="s">
         <v>449</v>
       </c>
       <c r="Q71" s="1" t="str">
@@ -7105,7 +7107,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
         <v>441</v>
       </c>
@@ -7136,7 +7138,7 @@
       <c r="O72" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="P72" s="6" t="s">
+      <c r="P72" s="1" t="s">
         <v>454</v>
       </c>
       <c r="Q72" s="1" t="str">
@@ -7144,7 +7146,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
         <v>441</v>
       </c>
@@ -7175,7 +7177,7 @@
       <c r="O73" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="P73" s="6" t="s">
+      <c r="P73" s="1" t="s">
         <v>457</v>
       </c>
       <c r="Q73" s="1" t="str">
@@ -7183,7 +7185,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
         <v>441</v>
       </c>
@@ -7214,7 +7216,7 @@
       <c r="O74" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="P74" s="6" t="s">
+      <c r="P74" s="1" t="s">
         <v>463</v>
       </c>
       <c r="Q74" s="1" t="str">
@@ -7222,7 +7224,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
         <v>441</v>
       </c>
@@ -7253,7 +7255,7 @@
       <c r="O75" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="P75" s="6" t="s">
+      <c r="P75" s="1" t="s">
         <v>469</v>
       </c>
       <c r="Q75" s="1" t="str">
@@ -7261,7 +7263,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
         <v>441</v>
       </c>
@@ -7275,79 +7277,79 @@
         <v>364</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>30</v>
+        <v>472</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>30</v>
+        <v>473</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="O76" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>476</v>
+        <v>477</v>
+      </c>
+      <c r="P76" s="1" t="s">
+        <v>478</v>
       </c>
       <c r="Q76" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P76))),MAX(Q$1:Q75)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
         <v>441</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>390</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="O77" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="P77" s="6" t="s">
-        <v>485</v>
+        <v>486</v>
+      </c>
+      <c r="P77" s="1" t="s">
+        <v>487</v>
       </c>
       <c r="Q77" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P77))),MAX(Q$1:Q76)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
         <v>441</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>364</v>
@@ -7365,28 +7367,28 @@
         <v>30</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O78" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="P78" s="6" t="s">
-        <v>488</v>
+      <c r="P78" s="1" t="s">
+        <v>490</v>
       </c>
       <c r="Q78" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P78))),MAX(Q$1:Q77)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
         <v>441</v>
       </c>
       <c r="B79" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>487</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>364</v>
@@ -7404,28 +7406,28 @@
         <v>30</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O79" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="P79" s="6" t="s">
-        <v>490</v>
+      <c r="P79" s="1" t="s">
+        <v>492</v>
       </c>
       <c r="Q79" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P79))),MAX(Q$1:Q78)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
         <v>441</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>364</v>
@@ -7443,25 +7445,25 @@
         <v>30</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O80" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="P80" s="6" t="s">
-        <v>492</v>
+      <c r="P80" s="1" t="s">
+        <v>494</v>
       </c>
       <c r="Q80" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P80))),MAX(Q$1:Q79)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
         <v>441</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>471</v>
@@ -7473,37 +7475,37 @@
         <v>30</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="O81" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="P81" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
+      </c>
+      <c r="P81" s="1" t="s">
+        <v>501</v>
       </c>
       <c r="Q81" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P81))),MAX(Q$1:Q80)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>458</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>364</v>
@@ -7521,28 +7523,28 @@
         <v>461</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="O82" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>504</v>
+        <v>505</v>
+      </c>
+      <c r="P82" s="1" t="s">
+        <v>506</v>
       </c>
       <c r="Q82" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P82))),MAX(Q$1:Q81)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>29</v>
@@ -7554,31 +7556,31 @@
         <v>30</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J83" s="1" t="s">
         <v>30</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="O83" s="5" t="s">
-        <v>509</v>
-      </c>
-      <c r="P83" s="6" t="s">
-        <v>510</v>
+        <v>511</v>
+      </c>
+      <c r="P83" s="1" t="s">
+        <v>512</v>
       </c>
       <c r="Q83" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P83))),MAX(Q$1:Q82)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>30</v>
@@ -7593,31 +7595,31 @@
         <v>30</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="O84" s="5" t="s">
-        <v>516</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>517</v>
+        <v>518</v>
+      </c>
+      <c r="P84" s="1" t="s">
+        <v>519</v>
       </c>
       <c r="Q84" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P84))),MAX(Q$1:Q83)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>30</v>
@@ -7638,25 +7640,25 @@
         <v>30</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="O85" s="5" t="s">
-        <v>520</v>
-      </c>
-      <c r="P85" s="6" t="s">
-        <v>521</v>
+        <v>522</v>
+      </c>
+      <c r="P85" s="1" t="s">
+        <v>523</v>
       </c>
       <c r="Q85" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P85))),MAX(Q$1:Q84)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>30</v>
@@ -7668,34 +7670,34 @@
         <v>30</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="O86" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
+      </c>
+      <c r="P86" s="1" t="s">
+        <v>530</v>
       </c>
       <c r="Q86" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P86))),MAX(Q$1:Q85)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>30</v>
@@ -7707,34 +7709,34 @@
         <v>30</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="O87" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="P87" s="6" t="s">
-        <v>536</v>
+        <v>537</v>
+      </c>
+      <c r="P87" s="1" t="s">
+        <v>538</v>
       </c>
       <c r="Q87" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P87))),MAX(Q$1:Q86)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>30</v>
@@ -7746,34 +7748,34 @@
         <v>30</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O88" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>543</v>
+        <v>544</v>
+      </c>
+      <c r="P88" s="1" t="s">
+        <v>545</v>
       </c>
       <c r="Q88" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P88))),MAX(Q$1:Q87)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>30</v>
@@ -7785,154 +7787,154 @@
         <v>30</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="O89" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="P89" s="6" t="s">
-        <v>549</v>
+        <v>529</v>
+      </c>
+      <c r="P89" s="1" t="s">
+        <v>551</v>
       </c>
       <c r="Q89" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P89))),MAX(Q$1:Q88)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="O90" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>558</v>
+        <v>537</v>
+      </c>
+      <c r="P90" s="1" t="s">
+        <v>560</v>
       </c>
       <c r="Q90" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P90))),MAX(Q$1:Q89)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="O91" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="P91" s="6" t="s">
-        <v>564</v>
+        <v>537</v>
+      </c>
+      <c r="P91" s="1" t="s">
+        <v>566</v>
       </c>
       <c r="Q91" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P91))),MAX(Q$1:Q90)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="O92" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="P92" s="6" t="s">
-        <v>570</v>
+        <v>544</v>
+      </c>
+      <c r="P92" s="1" t="s">
+        <v>572</v>
       </c>
       <c r="Q92" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P92))),MAX(Q$1:Q91)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>29</v>
@@ -7941,76 +7943,76 @@
         <v>30</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="O93" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="P93" s="6" t="s">
-        <v>575</v>
+        <v>544</v>
+      </c>
+      <c r="P93" s="1" t="s">
+        <v>577</v>
       </c>
       <c r="Q93" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P93))),MAX(Q$1:Q92)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="O94" s="5" t="s">
-        <v>582</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>583</v>
+        <v>584</v>
+      </c>
+      <c r="P94" s="1" t="s">
+        <v>585</v>
       </c>
       <c r="Q94" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P94))),MAX(Q$1:Q93)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>364</v>
@@ -8022,34 +8024,34 @@
         <v>30</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="O95" s="5" t="s">
-        <v>588</v>
-      </c>
-      <c r="P95" s="6" t="s">
-        <v>589</v>
+        <v>590</v>
+      </c>
+      <c r="P95" s="1" t="s">
+        <v>591</v>
       </c>
       <c r="Q95" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P95))),MAX(Q$1:Q94)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>364</v>
@@ -8061,34 +8063,34 @@
         <v>30</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="O96" s="5" t="s">
-        <v>588</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>594</v>
+        <v>590</v>
+      </c>
+      <c r="P96" s="1" t="s">
+        <v>596</v>
       </c>
       <c r="Q96" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P96))),MAX(Q$1:Q95)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>364</v>
@@ -8100,34 +8102,34 @@
         <v>30</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="O97" s="5" t="s">
-        <v>588</v>
-      </c>
-      <c r="P97" s="6" t="s">
-        <v>599</v>
+        <v>590</v>
+      </c>
+      <c r="P97" s="1" t="s">
+        <v>601</v>
       </c>
       <c r="Q97" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P97))),MAX(Q$1:Q96)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>364</v>
@@ -8139,330 +8141,330 @@
         <v>30</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="O98" s="5" t="s">
-        <v>605</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>606</v>
+        <v>607</v>
+      </c>
+      <c r="P98" s="1" t="s">
+        <v>608</v>
       </c>
       <c r="Q98" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P98))),MAX(Q$1:Q97)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="O99" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="P99" s="6" t="s">
-        <v>614</v>
+        <v>615</v>
+      </c>
+      <c r="P99" s="1" t="s">
+        <v>616</v>
       </c>
       <c r="Q99" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P99))),MAX(Q$1:Q98)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="O100" s="5" t="s">
-        <v>620</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>621</v>
+        <v>622</v>
+      </c>
+      <c r="P100" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="Q100" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P100))),MAX(Q$1:Q99)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="O101" s="5" t="s">
-        <v>628</v>
-      </c>
-      <c r="P101" s="6" t="s">
-        <v>629</v>
+        <v>630</v>
+      </c>
+      <c r="P101" s="1" t="s">
+        <v>631</v>
       </c>
       <c r="Q101" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P101))),MAX(Q$1:Q100)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="O102" s="5" t="s">
-        <v>636</v>
-      </c>
-      <c r="P102" s="6" t="s">
-        <v>637</v>
+        <v>638</v>
+      </c>
+      <c r="P102" s="1" t="s">
+        <v>639</v>
       </c>
       <c r="Q102" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P102))),MAX(Q$1:Q101)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="O103" s="5" t="s">
-        <v>644</v>
-      </c>
-      <c r="P103" s="6" t="s">
-        <v>645</v>
+        <v>646</v>
+      </c>
+      <c r="P103" s="1" t="s">
+        <v>647</v>
       </c>
       <c r="Q103" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P103))),MAX(Q$1:Q102)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="N104" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="O104" s="5" t="s">
-        <v>652</v>
-      </c>
-      <c r="P104" s="6" t="s">
-        <v>653</v>
+        <v>654</v>
+      </c>
+      <c r="P104" s="1" t="s">
+        <v>655</v>
       </c>
       <c r="Q104" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P104))),MAX(Q$1:Q103)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="O105" s="5" t="s">
-        <v>660</v>
-      </c>
-      <c r="P105" s="6" t="s">
-        <v>661</v>
+        <v>662</v>
+      </c>
+      <c r="P105" s="1" t="s">
+        <v>663</v>
       </c>
       <c r="Q105" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P105))),MAX(Q$1:Q104)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>129</v>
       </c>
       <c r="O106" s="5" t="s">
-        <v>665</v>
-      </c>
-      <c r="P106" s="6" t="s">
-        <v>666</v>
+        <v>667</v>
+      </c>
+      <c r="P106" s="1" t="s">
+        <v>668</v>
       </c>
       <c r="Q106" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P106))),MAX(Q$1:Q105)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="O107" s="5" t="s">
-        <v>671</v>
-      </c>
-      <c r="P107" s="6" t="s">
-        <v>672</v>
+        <v>673</v>
+      </c>
+      <c r="P107" s="1" t="s">
+        <v>674</v>
       </c>
       <c r="Q107" s="1" t="str">
         <f aca="false">IF(AND(Search!$B$2&lt;&gt;"",ISNUMBER(SEARCH(Search!$B$2,P107))),MAX(Q$1:Q106)+1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <autoFilter ref="A1:O107"/>
   <hyperlinks>
@@ -8540,7 +8542,7 @@
     <hyperlink ref="O73" r:id="rId72" location="nvidiatab-hw-documentation" display="https://networking-docs.nvidia.com/switches#nvidiatab-hw-documentation"/>
     <hyperlink ref="O74" r:id="rId73" location="nvidiatab-hw-documentation" display="https://networking-docs.nvidia.com/switches#nvidiatab-hw-documentation"/>
     <hyperlink ref="O75" r:id="rId74" location="nvidiatab-hw-documentation" display="https://networking-docs.nvidia.com/switches#nvidiatab-hw-documentation"/>
-    <hyperlink ref="O76" r:id="rId75" display="https://networking-docs.nvidia.com/skywayhw"/>
+    <hyperlink ref="O76" r:id="rId75" display="https://networking-docs.nvidia.com/skyway"/>
     <hyperlink ref="O77" r:id="rId76" display="https://networking-docs.nvidia.com/metrox3xc"/>
     <hyperlink ref="O78" r:id="rId77" location="nvidiatab-hw-documentation" display="https://networking-docs.nvidia.com/switches#nvidiatab-hw-documentation"/>
     <hyperlink ref="O79" r:id="rId78" location="nvidiatab-hw-documentation" display="https://networking-docs.nvidia.com/switches#nvidiatab-hw-documentation"/>
@@ -8569,9 +8571,9 @@
     <hyperlink ref="O102" r:id="rId101" display="https://networking-docs.nvidia.com/ufmenterprisendrhwum"/>
     <hyperlink ref="O103" r:id="rId102" display="https://networking-docs.nvidia.com/ufmsdn25apphw"/>
     <hyperlink ref="O104" r:id="rId103" display="https://networking-docs.nvidia.com/ufm45cyberaiapphw"/>
-    <hyperlink ref="O105" r:id="rId104" display="https://networking-docs.nvidia.com/connectx5enhw"/>
-    <hyperlink ref="O106" r:id="rId105" display="https://networking-docs.nvidia.com/connectx4vpihw"/>
-    <hyperlink ref="O107" r:id="rId106" display="https://networking-docs.nvidia.com/connectx4lxhw"/>
+    <hyperlink ref="O105" r:id="rId104" display="https://networking-docs.nvidia.com/connectx5en"/>
+    <hyperlink ref="O106" r:id="rId105" display="https://networking-docs.nvidia.com/connectx4"/>
+    <hyperlink ref="O107" r:id="rId106" display="https://networking-docs.nvidia.com/connectx4lx"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -8607,25 +8609,25 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="1" width="55"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>674</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="6" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>676</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B2" s="7"/>
+      <c r="C2" s="1" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>678</v>
+      </c>
+      <c r="B3" s="1" t="n">
         <f aca="false">MAX('All products'!$Q:$Q)</f>
         <v>0</v>
       </c>
@@ -8634,54 +8636,54 @@
         <v/>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="M5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="N5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="O5" s="9" t="s">
+      <c r="O5" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(1,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -8743,7 +8745,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(2,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -8805,7 +8807,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(3,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -8867,7 +8869,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(4,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -8929,7 +8931,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(5,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -8991,7 +8993,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(6,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -9053,7 +9055,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(7,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -9115,7 +9117,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(8,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -9177,7 +9179,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(9,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -9239,7 +9241,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(10,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -9301,7 +9303,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(11,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -9363,7 +9365,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(12,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -9425,7 +9427,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(13,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -9487,7 +9489,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(14,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -9549,7 +9551,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(15,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -9611,7 +9613,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(16,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -9673,7 +9675,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(17,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -9735,7 +9737,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(18,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -9797,7 +9799,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(19,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -9859,7 +9861,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(20,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -9921,7 +9923,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(21,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -9983,7 +9985,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(22,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -10045,7 +10047,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(23,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -10107,7 +10109,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(24,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -10169,7 +10171,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(25,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -10231,7 +10233,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(26,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -10293,7 +10295,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(27,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -10355,7 +10357,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(28,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -10417,7 +10419,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(29,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -10479,7 +10481,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(30,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -10541,7 +10543,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(31,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -10603,7 +10605,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(32,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -10665,7 +10667,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(33,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -10727,7 +10729,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(34,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -10789,7 +10791,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(35,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -10851,7 +10853,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(36,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -10913,7 +10915,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(37,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -10975,7 +10977,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(38,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -11037,7 +11039,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(39,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -11099,7 +11101,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(40,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -11161,7 +11163,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(41,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -11223,7 +11225,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(42,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -11285,7 +11287,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(43,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -11347,7 +11349,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(44,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -11409,7 +11411,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(45,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -11471,7 +11473,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(46,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -11533,7 +11535,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(47,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -11595,7 +11597,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(48,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -11657,7 +11659,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(49,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -11719,7 +11721,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(50,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -11781,7 +11783,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(51,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -11843,7 +11845,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(52,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -11905,7 +11907,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(53,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -11967,7 +11969,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(54,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -12029,7 +12031,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(55,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -12091,7 +12093,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(56,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -12153,7 +12155,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(57,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -12215,7 +12217,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(58,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -12277,7 +12279,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(59,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -12339,7 +12341,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(60,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -12401,7 +12403,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(61,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -12463,7 +12465,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(62,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -12525,7 +12527,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(63,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -12587,7 +12589,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(64,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -12649,7 +12651,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(65,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -12711,7 +12713,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(66,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -12773,7 +12775,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(67,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -12835,7 +12837,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(68,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -12897,7 +12899,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(69,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -12959,7 +12961,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(70,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -13021,7 +13023,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(71,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -13083,7 +13085,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(72,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -13145,7 +13147,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(73,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -13207,7 +13209,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(74,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -13269,7 +13271,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(75,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -13331,7 +13333,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(76,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -13393,7 +13395,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(77,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -13455,7 +13457,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(78,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -13517,7 +13519,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(79,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -13579,7 +13581,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(80,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -13641,7 +13643,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(81,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -13703,7 +13705,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(82,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -13765,7 +13767,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(83,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -13827,7 +13829,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(84,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -13889,7 +13891,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(85,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -13951,7 +13953,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(86,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -14013,7 +14015,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(87,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -14075,7 +14077,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(88,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -14137,7 +14139,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(89,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -14199,7 +14201,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(90,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -14261,7 +14263,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(91,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -14323,7 +14325,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(92,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -14385,7 +14387,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(93,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -14447,7 +14449,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(94,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -14509,7 +14511,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(95,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -14571,7 +14573,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(96,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -14633,7 +14635,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(97,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -14695,7 +14697,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(98,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -14757,7 +14759,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(99,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -14819,7 +14821,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(100,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -14881,7 +14883,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(101,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -14943,7 +14945,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(102,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -15005,7 +15007,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(103,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -15067,7 +15069,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(104,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -15129,7 +15131,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(105,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -15191,7 +15193,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(106,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -15253,7 +15255,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(107,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -15315,7 +15317,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(108,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -15377,7 +15379,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(109,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -15439,7 +15441,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(110,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -15501,7 +15503,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(111,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -15563,7 +15565,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(112,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -15625,7 +15627,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(113,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -15687,7 +15689,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(114,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -15749,7 +15751,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(115,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -15811,7 +15813,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(116,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -15873,7 +15875,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(117,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -15935,7 +15937,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(118,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -15997,7 +15999,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(119,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -16059,7 +16061,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(120,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -16121,7 +16123,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(121,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -16183,7 +16185,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(122,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -16245,7 +16247,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(123,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -16307,7 +16309,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(124,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -16369,7 +16371,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(125,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -16431,7 +16433,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(126,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -16493,7 +16495,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(127,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -16555,7 +16557,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(128,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -16617,7 +16619,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(129,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -16679,7 +16681,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(130,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -16741,7 +16743,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(131,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -16803,7 +16805,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(132,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -16865,7 +16867,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(133,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -16927,7 +16929,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(134,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -16989,7 +16991,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(135,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -17051,7 +17053,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(136,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -17113,7 +17115,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(137,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -17175,7 +17177,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(138,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -17237,7 +17239,7 @@
         <v/>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(139,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -17299,7 +17301,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(140,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -17361,7 +17363,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(141,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -17423,7 +17425,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(142,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -17485,7 +17487,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(143,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -17547,7 +17549,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(144,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -17609,7 +17611,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(145,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -17671,7 +17673,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(146,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -17733,7 +17735,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(147,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -17795,7 +17797,7 @@
         <v/>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(148,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -17857,7 +17859,7 @@
         <v/>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(149,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -17919,7 +17921,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(150,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -17981,7 +17983,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(151,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -18043,7 +18045,7 @@
         <v/>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(152,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -18105,7 +18107,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(153,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -18167,7 +18169,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(154,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -18229,7 +18231,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(155,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -18291,7 +18293,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(156,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -18353,7 +18355,7 @@
         <v/>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(157,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -18415,7 +18417,7 @@
         <v/>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(158,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -18477,7 +18479,7 @@
         <v/>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(159,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -18539,7 +18541,7 @@
         <v/>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(160,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -18601,7 +18603,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(161,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -18663,7 +18665,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(162,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -18725,7 +18727,7 @@
         <v/>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(163,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -18787,7 +18789,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(164,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -18849,7 +18851,7 @@
         <v/>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(165,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -18911,7 +18913,7 @@
         <v/>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(166,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -18973,7 +18975,7 @@
         <v/>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(167,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -19035,7 +19037,7 @@
         <v/>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(168,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -19097,7 +19099,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(169,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -19159,7 +19161,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(170,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -19221,7 +19223,7 @@
         <v/>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(171,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -19283,7 +19285,7 @@
         <v/>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(172,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -19345,7 +19347,7 @@
         <v/>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(173,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -19407,7 +19409,7 @@
         <v/>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(174,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -19469,7 +19471,7 @@
         <v/>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(175,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -19531,7 +19533,7 @@
         <v/>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(176,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -19593,7 +19595,7 @@
         <v/>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(177,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -19655,7 +19657,7 @@
         <v/>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(178,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -19717,7 +19719,7 @@
         <v/>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(179,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -19779,7 +19781,7 @@
         <v/>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(180,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -19841,7 +19843,7 @@
         <v/>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(181,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -19903,7 +19905,7 @@
         <v/>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(182,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -19965,7 +19967,7 @@
         <v/>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(183,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -20027,7 +20029,7 @@
         <v/>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(184,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -20089,7 +20091,7 @@
         <v/>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(185,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -20151,7 +20153,7 @@
         <v/>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(186,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -20213,7 +20215,7 @@
         <v/>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(187,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -20275,7 +20277,7 @@
         <v/>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(188,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -20337,7 +20339,7 @@
         <v/>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(189,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -20399,7 +20401,7 @@
         <v/>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(190,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -20461,7 +20463,7 @@
         <v/>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(191,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -20523,7 +20525,7 @@
         <v/>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(192,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -20585,7 +20587,7 @@
         <v/>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(193,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -20647,7 +20649,7 @@
         <v/>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(194,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -20709,7 +20711,7 @@
         <v/>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(195,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -20771,7 +20773,7 @@
         <v/>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(196,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -20833,7 +20835,7 @@
         <v/>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(197,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -20895,7 +20897,7 @@
         <v/>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(198,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -20957,7 +20959,7 @@
         <v/>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(199,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -21019,7 +21021,7 @@
         <v/>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="str">
         <f aca="false">IFERROR(INDEX('All products'!$A$2:$A$107,MATCH(200,'All products'!$Q$2:$Q$107,0))&amp;"","")</f>
         <v/>
@@ -21115,7 +21117,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="58"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
@@ -21156,7 +21158,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>27</v>
       </c>
@@ -21197,7 +21199,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
@@ -21238,7 +21240,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>45</v>
       </c>
@@ -21279,7 +21281,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>45</v>
       </c>
@@ -21320,7 +21322,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>55</v>
       </c>
@@ -21361,7 +21363,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>55</v>
       </c>
@@ -21402,7 +21404,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>62</v>
       </c>
@@ -21443,7 +21445,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>62</v>
       </c>
@@ -21484,7 +21486,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>72</v>
       </c>
@@ -21525,7 +21527,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>72</v>
       </c>
@@ -21566,7 +21568,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>82</v>
       </c>
@@ -21607,7 +21609,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>92</v>
       </c>
@@ -21648,7 +21650,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>98</v>
       </c>
@@ -21689,7 +21691,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>104</v>
       </c>
@@ -21730,7 +21732,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>109</v>
       </c>
@@ -21771,7 +21773,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>115</v>
       </c>
@@ -21812,7 +21814,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>120</v>
       </c>
@@ -21853,7 +21855,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>126</v>
       </c>
@@ -21894,7 +21896,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>134</v>
       </c>
@@ -21935,7 +21937,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>141</v>
       </c>
@@ -21976,7 +21978,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>150</v>
       </c>
@@ -22017,7 +22019,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>156</v>
       </c>
@@ -22058,7 +22060,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>162</v>
       </c>
@@ -22099,7 +22101,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>166</v>
       </c>
@@ -22140,7 +22142,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>172</v>
       </c>
@@ -22181,7 +22183,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>177</v>
       </c>
@@ -22222,7 +22224,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>180</v>
       </c>
@@ -22263,7 +22265,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>185</v>
       </c>
@@ -22304,7 +22306,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>190</v>
       </c>
@@ -22345,7 +22347,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>195</v>
       </c>
@@ -22386,7 +22388,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>201</v>
       </c>
@@ -22427,7 +22429,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>208</v>
       </c>
@@ -22468,7 +22470,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>213</v>
       </c>
@@ -22509,7 +22511,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>220</v>
       </c>
@@ -22621,7 +22623,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="51"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
@@ -22662,7 +22664,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>228</v>
       </c>
@@ -22703,7 +22705,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>238</v>
       </c>
@@ -22744,7 +22746,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>244</v>
       </c>
@@ -22826,7 +22828,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="59"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
@@ -22867,7 +22869,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>252</v>
       </c>
@@ -22908,7 +22910,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>262</v>
       </c>
@@ -22949,7 +22951,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>270</v>
       </c>
@@ -22990,7 +22992,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>279</v>
       </c>
@@ -23031,7 +23033,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>287</v>
       </c>
@@ -23072,7 +23074,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>292</v>
       </c>
@@ -23113,7 +23115,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>298</v>
       </c>
@@ -23154,7 +23156,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>304</v>
       </c>
@@ -23195,7 +23197,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>308</v>
       </c>
@@ -23236,7 +23238,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>315</v>
       </c>
@@ -23277,7 +23279,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>321</v>
       </c>
@@ -23361,9 +23363,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="58"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>10</v>
@@ -23387,7 +23389,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>329</v>
       </c>
@@ -23413,7 +23415,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>333</v>
       </c>
@@ -23439,7 +23441,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>333</v>
       </c>
@@ -23465,7 +23467,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>343</v>
       </c>
@@ -23491,7 +23493,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>343</v>
       </c>
@@ -23517,7 +23519,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>343</v>
       </c>
@@ -23543,7 +23545,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>343</v>
       </c>
@@ -23610,7 +23612,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="45"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
@@ -23630,7 +23632,7 @@
         <v>16</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>22</v>
@@ -23639,7 +23641,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>362</v>
       </c>
@@ -23668,7 +23670,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>370</v>
       </c>
@@ -23697,7 +23699,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>375</v>
       </c>
@@ -23726,7 +23728,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>379</v>
       </c>
@@ -23755,7 +23757,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>382</v>
       </c>
@@ -23784,7 +23786,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>389</v>
       </c>
@@ -23813,7 +23815,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>395</v>
       </c>
@@ -23842,7 +23844,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>398</v>
       </c>
@@ -23871,7 +23873,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>404</v>
       </c>
@@ -23900,7 +23902,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>413</v>
       </c>
@@ -23929,7 +23931,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>419</v>
       </c>
@@ -23958,7 +23960,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>427</v>
       </c>
@@ -23987,7 +23989,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>435</v>
       </c>
@@ -24016,7 +24018,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>437</v>
       </c>
@@ -24045,7 +24047,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <autoFilter ref="A1:I15"/>
   <hyperlinks>
@@ -24091,7 +24093,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="1" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
@@ -24111,7 +24113,7 @@
         <v>16</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>22</v>
@@ -24120,7 +24122,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>442</v>
       </c>
@@ -24149,7 +24151,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>450</v>
       </c>
@@ -24178,7 +24180,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>455</v>
       </c>
@@ -24207,7 +24209,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>458</v>
       </c>
@@ -24236,7 +24238,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>464</v>
       </c>
@@ -24265,7 +24267,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>470</v>
       </c>
@@ -24276,59 +24278,59 @@
         <v>364</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>30</v>
+        <v>472</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>30</v>
+        <v>473</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>390</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>364</v>
@@ -24346,18 +24348,18 @@
         <v>30</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>487</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>364</v>
@@ -24375,18 +24377,18 @@
         <v>30</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>364</v>
@@ -24404,15 +24406,15 @@
         <v>30</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>471</v>
@@ -24424,19 +24426,19 @@
         <v>30</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -24447,7 +24449,7 @@
     <hyperlink ref="I4" r:id="rId3" location="nvidiatab-hw-documentation" display="https://networking-docs.nvidia.com/switches#nvidiatab-hw-documentation"/>
     <hyperlink ref="I5" r:id="rId4" location="nvidiatab-hw-documentation" display="https://networking-docs.nvidia.com/switches#nvidiatab-hw-documentation"/>
     <hyperlink ref="I6" r:id="rId5" location="nvidiatab-hw-documentation" display="https://networking-docs.nvidia.com/switches#nvidiatab-hw-documentation"/>
-    <hyperlink ref="I7" r:id="rId6" display="https://networking-docs.nvidia.com/skywayhw"/>
+    <hyperlink ref="I7" r:id="rId6" display="https://networking-docs.nvidia.com/skyway"/>
     <hyperlink ref="I8" r:id="rId7" display="https://networking-docs.nvidia.com/metrox3xc"/>
     <hyperlink ref="I9" r:id="rId8" location="nvidiatab-hw-documentation" display="https://networking-docs.nvidia.com/switches#nvidiatab-hw-documentation"/>
     <hyperlink ref="I10" r:id="rId9" location="nvidiatab-hw-documentation" display="https://networking-docs.nvidia.com/switches#nvidiatab-hw-documentation"/>
